--- a/LISTAS/ma/PARKER.xlsx
+++ b/LISTAS/ma/PARKER.xlsx
@@ -819,14 +819,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45173.57050632545</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="20">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,8 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="20">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -860,14 +854,6 @@
     <row r="12" ht="41.25" customHeight="1" s="20">
       <c r="A12" s="22" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="22.5" customHeight="1" s="20">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -911,7 +897,7 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="7" t="n">
-        <v>594.197</v>
+        <v>617.965</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="20">
@@ -927,7 +913,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="8" t="n">
-        <v>613.921</v>
+        <v>638.478</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="20">
@@ -943,7 +929,7 @@
       </c>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="7" t="n">
-        <v>631.176</v>
+        <v>656.423</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="20">
@@ -959,7 +945,7 @@
       </c>
       <c r="C27" s="18" t="n"/>
       <c r="D27" s="8" t="n">
-        <v>673.83</v>
+        <v>700.783</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="20">
@@ -975,7 +961,7 @@
       </c>
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="7" t="n">
-        <v>820.285</v>
+        <v>853.096</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="20">
@@ -991,7 +977,7 @@
       </c>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="8" t="n">
-        <v>961.561</v>
+        <v>1000.023</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="20">
@@ -1007,7 +993,7 @@
       </c>
       <c r="C30" s="18" t="n"/>
       <c r="D30" s="8" t="n">
-        <v>1099.628</v>
+        <v>1143.613</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="20">
@@ -1023,7 +1009,7 @@
       </c>
       <c r="C31" s="18" t="n"/>
       <c r="D31" s="7" t="n">
-        <v>1188.388</v>
+        <v>1235.924</v>
       </c>
       <c r="E31" s="2" t="n"/>
     </row>
@@ -1071,7 +1057,7 @@
       </c>
       <c r="C36" s="18" t="n"/>
       <c r="D36" s="7" t="n">
-        <v>760.62</v>
+        <v>791.045</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="20">
@@ -1087,7 +1073,7 @@
       </c>
       <c r="C37" s="18" t="n"/>
       <c r="D37" s="8" t="n">
-        <v>835.323</v>
+        <v>868.736</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="20">
@@ -1103,7 +1089,7 @@
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="7" t="n">
-        <v>884.6319999999999</v>
+        <v>920.0170000000001</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="20">
@@ -1119,7 +1105,7 @@
       </c>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="8" t="n">
-        <v>938.138</v>
+        <v>975.664</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="20">
@@ -1135,7 +1121,7 @@
       </c>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="7" t="n">
-        <v>1047.855</v>
+        <v>1089.769</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="20">
@@ -1151,7 +1137,7 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="8" t="n">
-        <v>1360.978</v>
+        <v>1415.417</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="20">
@@ -1167,7 +1153,7 @@
       </c>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="7" t="n">
-        <v>1375.77</v>
+        <v>1430.801</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="20">
@@ -1183,7 +1169,7 @@
       </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="8" t="n">
-        <v>1410.288</v>
+        <v>1466.7</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="20">
@@ -1199,7 +1185,7 @@
       </c>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="7" t="n">
-        <v>1799.845</v>
+        <v>1871.839</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="20">
@@ -1215,7 +1201,7 @@
       </c>
       <c r="C45" s="18" t="n"/>
       <c r="D45" s="8" t="n">
-        <v>2112.968</v>
+        <v>2197.487</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="20">
@@ -1231,7 +1217,7 @@
       </c>
       <c r="C46" s="18" t="n"/>
       <c r="D46" s="7" t="n">
-        <v>2588.818</v>
+        <v>2692.371</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="20">
@@ -1247,10 +1233,9 @@
       </c>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="7" t="n">
-        <v>2963.574</v>
-      </c>
-    </row>
-    <row r="48"/>
+        <v>3082.117</v>
+      </c>
+    </row>
     <row r="49" ht="23.25" customHeight="1" s="20">
       <c r="A49" s="24" t="inlineStr">
         <is>
@@ -1258,7 +1243,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="18" customHeight="1" s="20">
       <c r="A51" s="9" t="inlineStr">
         <is>
@@ -1290,7 +1274,7 @@
       </c>
       <c r="C52" s="18" t="n"/>
       <c r="D52" s="7" t="n">
-        <v>811.163</v>
+        <v>843.61</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="20">
@@ -1306,7 +1290,7 @@
       </c>
       <c r="C53" s="18" t="n"/>
       <c r="D53" s="8" t="n">
-        <v>976.352</v>
+        <v>1015.406</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="20">
@@ -1322,7 +1306,7 @@
       </c>
       <c r="C54" s="18" t="n"/>
       <c r="D54" s="7" t="n">
-        <v>1072.511</v>
+        <v>1115.411</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="20">
@@ -1338,7 +1322,7 @@
       </c>
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="8" t="n">
-        <v>1168.667</v>
+        <v>1215.414</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="20">
@@ -1354,7 +1338,7 @@
       </c>
       <c r="C56" s="18" t="n"/>
       <c r="D56" s="7" t="n">
-        <v>1269.753</v>
+        <v>1320.543</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="20">
@@ -1370,7 +1354,7 @@
       </c>
       <c r="C57" s="18" t="n"/>
       <c r="D57" s="8" t="n">
-        <v>1410.288</v>
+        <v>1466.7</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="20">
@@ -1386,7 +1370,7 @@
       </c>
       <c r="C58" s="18" t="n"/>
       <c r="D58" s="7" t="n">
-        <v>1516.309</v>
+        <v>1576.961</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="20">
@@ -1402,7 +1386,7 @@
       </c>
       <c r="C59" s="18" t="n"/>
       <c r="D59" s="8" t="n">
-        <v>1644.516</v>
+        <v>1710.297</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="20">
@@ -1418,7 +1402,7 @@
       </c>
       <c r="C60" s="18" t="n"/>
       <c r="D60" s="7" t="n">
-        <v>2430.528</v>
+        <v>2527.749</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="20">
@@ -1434,7 +1418,7 @@
       </c>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="8" t="n">
-        <v>2630.733</v>
+        <v>2735.962</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="20">
@@ -1450,7 +1434,7 @@
       </c>
       <c r="C62" s="18" t="n"/>
       <c r="D62" s="7" t="n">
-        <v>2926.595</v>
+        <v>3043.659</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1" s="20">
@@ -1466,10 +1450,9 @@
       </c>
       <c r="C63" s="18" t="n"/>
       <c r="D63" s="7" t="n">
-        <v>3510.93</v>
-      </c>
-    </row>
-    <row r="64"/>
+        <v>3651.367</v>
+      </c>
+    </row>
     <row r="65" ht="23.25" customHeight="1" s="20">
       <c r="A65" s="24" t="inlineStr">
         <is>
@@ -1477,7 +1460,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="18" customHeight="1" s="20">
       <c r="A67" s="9" t="inlineStr">
         <is>
@@ -1509,7 +1491,7 @@
       </c>
       <c r="C68" s="18" t="n"/>
       <c r="D68" s="7" t="n">
-        <v>974.383</v>
+        <v>1013.358</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="20">
@@ -1525,7 +1507,7 @@
       </c>
       <c r="C69" s="18" t="n"/>
       <c r="D69" s="8" t="n">
-        <v>1120.338</v>
+        <v>1165.152</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="20">
@@ -1541,7 +1523,7 @@
       </c>
       <c r="C70" s="18" t="n"/>
       <c r="D70" s="7" t="n">
-        <v>1168.667</v>
+        <v>1215.414</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="20">
@@ -1557,7 +1539,7 @@
       </c>
       <c r="C71" s="18" t="n"/>
       <c r="D71" s="8" t="n">
-        <v>1269.753</v>
+        <v>1320.543</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="20">
@@ -1573,7 +1555,7 @@
       </c>
       <c r="C72" s="18" t="n"/>
       <c r="D72" s="7" t="n">
-        <v>1445.548</v>
+        <v>1503.37</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="20">
@@ -1589,7 +1571,7 @@
       </c>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="8" t="n">
-        <v>1563.151</v>
+        <v>1625.677</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="20">
@@ -1605,7 +1587,7 @@
       </c>
       <c r="C74" s="18" t="n"/>
       <c r="D74" s="7" t="n">
-        <v>1713.55</v>
+        <v>1782.092</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="20">
@@ -1621,7 +1603,7 @@
       </c>
       <c r="C75" s="18" t="n"/>
       <c r="D75" s="8" t="n">
-        <v>1903.887</v>
+        <v>1980.042</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="20">
@@ -1637,7 +1619,7 @@
       </c>
       <c r="C76" s="18" t="n"/>
       <c r="D76" s="7" t="n">
-        <v>2574.022</v>
+        <v>2676.983</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="20">
@@ -1653,7 +1635,7 @@
       </c>
       <c r="C77" s="18" t="n"/>
       <c r="D77" s="8" t="n">
-        <v>3017.82</v>
+        <v>3138.533</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" s="20">
@@ -1669,7 +1651,7 @@
       </c>
       <c r="C78" s="18" t="n"/>
       <c r="D78" s="7" t="n">
-        <v>3533.114</v>
+        <v>3674.439</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="20">
@@ -1685,7 +1667,7 @@
       </c>
       <c r="C79" s="18" t="n"/>
       <c r="D79" s="7" t="n">
-        <v>3809.254</v>
+        <v>3961.624</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="20">
@@ -1701,10 +1683,9 @@
       </c>
       <c r="C80" s="18" t="n"/>
       <c r="D80" s="7" t="n">
-        <v>3888.429</v>
-      </c>
-    </row>
-    <row r="81"/>
+        <v>4043.966</v>
+      </c>
+    </row>
     <row r="82" ht="23.25" customHeight="1" s="20">
       <c r="A82" s="24" t="inlineStr">
         <is>
@@ -1712,7 +1693,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84" ht="18" customHeight="1" s="20">
       <c r="A84" s="9" t="inlineStr">
         <is>
@@ -1744,7 +1724,7 @@
       </c>
       <c r="C85" s="18" t="n"/>
       <c r="D85" s="7" t="n">
-        <v>1362.209</v>
+        <v>1416.697</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1" s="20">
@@ -1760,7 +1740,7 @@
       </c>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="8" t="n">
-        <v>1582.878</v>
+        <v>1646.193</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1" s="20">
@@ -1776,7 +1756,7 @@
       </c>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="7" t="n">
-        <v>1765.82</v>
+        <v>1836.453</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1" s="20">
@@ -1792,7 +1772,7 @@
       </c>
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="8" t="n">
-        <v>1945.31</v>
+        <v>2023.122</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1" s="20">
@@ -1808,7 +1788,7 @@
       </c>
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="7" t="n">
-        <v>2332.401</v>
+        <v>2425.697</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="20">
@@ -1824,7 +1804,7 @@
       </c>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="8" t="n">
-        <v>2441.377</v>
+        <v>2539.032</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="20">
@@ -1840,7 +1820,7 @@
       </c>
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="7" t="n">
-        <v>2879.749</v>
+        <v>2994.939</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="20">
@@ -1856,7 +1836,7 @@
       </c>
       <c r="C92" s="18" t="n"/>
       <c r="D92" s="8" t="n">
-        <v>3229.855</v>
+        <v>3359.049</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="20">
@@ -1872,7 +1852,7 @@
       </c>
       <c r="C93" s="18" t="n"/>
       <c r="D93" s="7" t="n">
-        <v>3821.585</v>
+        <v>3974.448</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="20">
@@ -1888,7 +1868,7 @@
       </c>
       <c r="C94" s="18" t="n"/>
       <c r="D94" s="8" t="n">
-        <v>4312.225</v>
+        <v>4484.714</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="20">
@@ -1904,7 +1884,7 @@
       </c>
       <c r="C95" s="18" t="n"/>
       <c r="D95" s="7" t="n">
-        <v>5268.854</v>
+        <v>5479.608</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="20">
@@ -1920,10 +1900,9 @@
       </c>
       <c r="C96" s="18" t="n"/>
       <c r="D96" s="7" t="n">
-        <v>7260.379</v>
-      </c>
-    </row>
-    <row r="97"/>
+        <v>7550.794</v>
+      </c>
+    </row>
     <row r="98" ht="23.25" customHeight="1" s="20">
       <c r="A98" s="24" t="inlineStr">
         <is>
@@ -1931,7 +1910,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100" ht="18" customHeight="1" s="20">
       <c r="A100" s="9" t="inlineStr">
         <is>
@@ -1963,7 +1941,7 @@
       </c>
       <c r="C101" s="18" t="n"/>
       <c r="D101" s="7" t="n">
-        <v>2061.19</v>
+        <v>2143.638</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1" s="20">
@@ -1979,7 +1957,7 @@
       </c>
       <c r="C102" s="18" t="n"/>
       <c r="D102" s="8" t="n">
-        <v>2332.401</v>
+        <v>2425.697</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1" s="20">
@@ -1995,7 +1973,7 @@
       </c>
       <c r="C103" s="18" t="n"/>
       <c r="D103" s="7" t="n">
-        <v>2633.193</v>
+        <v>2738.521</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1" s="20">
@@ -2011,7 +1989,7 @@
       </c>
       <c r="C104" s="18" t="n"/>
       <c r="D104" s="8" t="n">
-        <v>3121.373</v>
+        <v>3246.228</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1" s="20">
@@ -2027,7 +2005,7 @@
       </c>
       <c r="C105" s="18" t="n"/>
       <c r="D105" s="7" t="n">
-        <v>3155.889</v>
+        <v>3282.125</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1" s="20">
@@ -2043,7 +2021,7 @@
       </c>
       <c r="C106" s="18" t="n"/>
       <c r="D106" s="8" t="n">
-        <v>3986.773</v>
+        <v>4146.244</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1" s="20">
@@ -2059,7 +2037,7 @@
       </c>
       <c r="C107" s="18" t="n"/>
       <c r="D107" s="7" t="n">
-        <v>4487.281</v>
+        <v>4666.772</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1" s="20">
@@ -2075,7 +2053,7 @@
       </c>
       <c r="C108" s="18" t="n"/>
       <c r="D108" s="8" t="n">
-        <v>5066.686</v>
+        <v>5269.353</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1" s="20">
@@ -2091,7 +2069,7 @@
       </c>
       <c r="C109" s="18" t="n"/>
       <c r="D109" s="7" t="n">
-        <v>5867.981</v>
+        <v>6102.7</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="20">
@@ -2107,10 +2085,9 @@
       </c>
       <c r="C110" s="18" t="n"/>
       <c r="D110" s="8" t="n">
-        <v>7478.241</v>
-      </c>
-    </row>
-    <row r="111"/>
+        <v>7777.371</v>
+      </c>
+    </row>
     <row r="112" ht="23.25" customHeight="1" s="20">
       <c r="A112" s="24" t="inlineStr">
         <is>
@@ -2118,7 +2095,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114" ht="18" customHeight="1" s="20">
       <c r="A114" s="9" t="inlineStr">
         <is>
@@ -2150,7 +2126,7 @@
       </c>
       <c r="C115" s="18" t="n"/>
       <c r="D115" s="7" t="n">
-        <v>2957.415</v>
+        <v>3075.712</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="20">
@@ -2166,7 +2142,7 @@
       </c>
       <c r="C116" s="18" t="n"/>
       <c r="D116" s="8" t="n">
-        <v>3269.306</v>
+        <v>3400.078</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="20">
@@ -2182,7 +2158,7 @@
       </c>
       <c r="C117" s="18" t="n"/>
       <c r="D117" s="7" t="n">
-        <v>3796.93</v>
+        <v>3948.807</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1" s="20">
@@ -2198,7 +2174,7 @@
       </c>
       <c r="C118" s="18" t="n"/>
       <c r="D118" s="8" t="n">
-        <v>3942.395</v>
+        <v>4100.091</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="20">
@@ -2214,7 +2190,7 @@
       </c>
       <c r="C119" s="18" t="n"/>
       <c r="D119" s="7" t="n">
-        <v>4437.966</v>
+        <v>4615.485</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1" s="20">
@@ -2230,7 +2206,7 @@
       </c>
       <c r="C120" s="18" t="n"/>
       <c r="D120" s="8" t="n">
-        <v>5172.699</v>
+        <v>5379.607</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1" s="20">
@@ -2246,7 +2222,7 @@
       </c>
       <c r="C121" s="18" t="n"/>
       <c r="D121" s="7" t="n">
-        <v>6040.569</v>
+        <v>6282.192</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1" s="20">
@@ -2262,7 +2238,7 @@
       </c>
       <c r="C122" s="18" t="n"/>
       <c r="D122" s="8" t="n">
-        <v>6829.54</v>
+        <v>7102.722</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1" s="20">
@@ -2278,7 +2254,7 @@
       </c>
       <c r="C123" s="18" t="n"/>
       <c r="D123" s="7" t="n">
-        <v>7421.269</v>
+        <v>7718.12</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="20">
@@ -2294,11 +2270,9 @@
       </c>
       <c r="C124" s="18" t="n"/>
       <c r="D124" s="8" t="n">
-        <v>10018.71</v>
-      </c>
-    </row>
-    <row r="125"/>
-    <row r="126"/>
+        <v>10419.458</v>
+      </c>
+    </row>
     <row r="127" ht="20.25" customHeight="1" s="20">
       <c r="A127" s="14" t="inlineStr">
         <is>
@@ -2324,102 +2298,102 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B119:C119"/>
     <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B84:C84"/>
     <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
     <mergeCell ref="B121:C121"/>
     <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B114:C114"/>
     <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B110:C110"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
     <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PARKER.xlsx
+++ b/LISTAS/ma/PARKER.xlsx
@@ -819,7 +819,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/PARKER.xlsx
+++ b/LISTAS/ma/PARKER.xlsx
@@ -819,7 +819,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/PARKER.xlsx
+++ b/LISTAS/ma/PARKER.xlsx
@@ -819,10 +819,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
+        <v>45264.54808382592</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="20">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -844,6 +848,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="20">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -854,6 +860,14 @@
     <row r="12" ht="41.25" customHeight="1" s="20">
       <c r="A12" s="22" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="22.5" customHeight="1" s="20">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -897,7 +911,7 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="7" t="n">
-        <v>617.965</v>
+        <v>867.28</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="20">
@@ -913,7 +927,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="8" t="n">
-        <v>638.478</v>
+        <v>896.0700000000001</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="20">
@@ -929,7 +943,7 @@
       </c>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="7" t="n">
-        <v>656.423</v>
+        <v>921.26</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="20">
@@ -945,7 +959,7 @@
       </c>
       <c r="C27" s="18" t="n"/>
       <c r="D27" s="8" t="n">
-        <v>700.783</v>
+        <v>983.52</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="20">
@@ -961,7 +975,7 @@
       </c>
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="7" t="n">
-        <v>853.096</v>
+        <v>1197.28</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="20">
@@ -977,7 +991,7 @@
       </c>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="8" t="n">
-        <v>1000.023</v>
+        <v>1403.49</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="20">
@@ -993,7 +1007,7 @@
       </c>
       <c r="C30" s="18" t="n"/>
       <c r="D30" s="8" t="n">
-        <v>1143.613</v>
+        <v>1605.01</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="20">
@@ -1009,7 +1023,7 @@
       </c>
       <c r="C31" s="18" t="n"/>
       <c r="D31" s="7" t="n">
-        <v>1235.924</v>
+        <v>1734.57</v>
       </c>
       <c r="E31" s="2" t="n"/>
     </row>
@@ -1057,7 +1071,7 @@
       </c>
       <c r="C36" s="18" t="n"/>
       <c r="D36" s="7" t="n">
-        <v>791.045</v>
+        <v>1110.2</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="20">
@@ -1073,7 +1087,7 @@
       </c>
       <c r="C37" s="18" t="n"/>
       <c r="D37" s="8" t="n">
-        <v>868.736</v>
+        <v>1219.23</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="20">
@@ -1089,7 +1103,7 @@
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="7" t="n">
-        <v>920.0170000000001</v>
+        <v>1291.2</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="20">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="8" t="n">
-        <v>975.664</v>
+        <v>1369.3</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="20">
@@ -1121,7 +1135,7 @@
       </c>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="7" t="n">
-        <v>1089.769</v>
+        <v>1529.44</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="20">
@@ -1137,7 +1151,7 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="8" t="n">
-        <v>1415.417</v>
+        <v>1986.48</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="20">
@@ -1153,7 +1167,7 @@
       </c>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="7" t="n">
-        <v>1430.801</v>
+        <v>2008.07</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="20">
@@ -1169,7 +1183,7 @@
       </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="8" t="n">
-        <v>1466.7</v>
+        <v>2058.45</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="20">
@@ -1185,7 +1199,7 @@
       </c>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="7" t="n">
-        <v>1871.839</v>
+        <v>2627.05</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="20">
@@ -1201,7 +1215,7 @@
       </c>
       <c r="C45" s="18" t="n"/>
       <c r="D45" s="8" t="n">
-        <v>2197.487</v>
+        <v>3084.08</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="20">
@@ -1217,7 +1231,7 @@
       </c>
       <c r="C46" s="18" t="n"/>
       <c r="D46" s="7" t="n">
-        <v>2692.371</v>
+        <v>3778.63</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="20">
@@ -1233,9 +1247,10 @@
       </c>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="7" t="n">
-        <v>3082.117</v>
-      </c>
-    </row>
+        <v>4325.62</v>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49" ht="23.25" customHeight="1" s="20">
       <c r="A49" s="24" t="inlineStr">
         <is>
@@ -1243,6 +1258,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51" ht="18" customHeight="1" s="20">
       <c r="A51" s="9" t="inlineStr">
         <is>
@@ -1274,7 +1290,7 @@
       </c>
       <c r="C52" s="18" t="n"/>
       <c r="D52" s="7" t="n">
-        <v>843.61</v>
+        <v>1183.97</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="20">
@@ -1290,7 +1306,7 @@
       </c>
       <c r="C53" s="18" t="n"/>
       <c r="D53" s="8" t="n">
-        <v>1015.406</v>
+        <v>1425.08</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="20">
@@ -1306,7 +1322,7 @@
       </c>
       <c r="C54" s="18" t="n"/>
       <c r="D54" s="7" t="n">
-        <v>1115.411</v>
+        <v>1565.43</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="20">
@@ -1322,7 +1338,7 @@
       </c>
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="8" t="n">
-        <v>1215.414</v>
+        <v>1705.78</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="20">
@@ -1338,7 +1354,7 @@
       </c>
       <c r="C56" s="18" t="n"/>
       <c r="D56" s="7" t="n">
-        <v>1320.543</v>
+        <v>1853.33</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="20">
@@ -1354,7 +1370,7 @@
       </c>
       <c r="C57" s="18" t="n"/>
       <c r="D57" s="8" t="n">
-        <v>1466.7</v>
+        <v>2058.45</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="20">
@@ -1370,7 +1386,7 @@
       </c>
       <c r="C58" s="18" t="n"/>
       <c r="D58" s="7" t="n">
-        <v>1576.961</v>
+        <v>2213.2</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="20">
@@ -1386,7 +1402,7 @@
       </c>
       <c r="C59" s="18" t="n"/>
       <c r="D59" s="8" t="n">
-        <v>1710.297</v>
+        <v>2400.33</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="20">
@@ -1402,7 +1418,7 @@
       </c>
       <c r="C60" s="18" t="n"/>
       <c r="D60" s="7" t="n">
-        <v>2527.749</v>
+        <v>3547.59</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="20">
@@ -1418,7 +1434,7 @@
       </c>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="8" t="n">
-        <v>2735.962</v>
+        <v>3839.81</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="20">
@@ -1434,7 +1450,7 @@
       </c>
       <c r="C62" s="18" t="n"/>
       <c r="D62" s="7" t="n">
-        <v>3043.659</v>
+        <v>4271.65</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1" s="20">
@@ -1450,9 +1466,10 @@
       </c>
       <c r="C63" s="18" t="n"/>
       <c r="D63" s="7" t="n">
-        <v>3651.367</v>
-      </c>
-    </row>
+        <v>5124.54</v>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65" ht="23.25" customHeight="1" s="20">
       <c r="A65" s="24" t="inlineStr">
         <is>
@@ -1460,6 +1477,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67" ht="18" customHeight="1" s="20">
       <c r="A67" s="9" t="inlineStr">
         <is>
@@ -1491,7 +1509,7 @@
       </c>
       <c r="C68" s="18" t="n"/>
       <c r="D68" s="7" t="n">
-        <v>1013.358</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="20">
@@ -1507,7 +1525,7 @@
       </c>
       <c r="C69" s="18" t="n"/>
       <c r="D69" s="8" t="n">
-        <v>1165.152</v>
+        <v>1635.24</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="20">
@@ -1523,7 +1541,7 @@
       </c>
       <c r="C70" s="18" t="n"/>
       <c r="D70" s="7" t="n">
-        <v>1215.414</v>
+        <v>1705.78</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="20">
@@ -1539,7 +1557,7 @@
       </c>
       <c r="C71" s="18" t="n"/>
       <c r="D71" s="8" t="n">
-        <v>1320.543</v>
+        <v>1853.33</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="20">
@@ -1555,7 +1573,7 @@
       </c>
       <c r="C72" s="18" t="n"/>
       <c r="D72" s="7" t="n">
-        <v>1503.37</v>
+        <v>2109.92</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="20">
@@ -1571,7 +1589,7 @@
       </c>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="8" t="n">
-        <v>1625.677</v>
+        <v>2281.57</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="20">
@@ -1587,7 +1605,7 @@
       </c>
       <c r="C74" s="18" t="n"/>
       <c r="D74" s="7" t="n">
-        <v>1782.092</v>
+        <v>2501.09</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="20">
@@ -1603,7 +1621,7 @@
       </c>
       <c r="C75" s="18" t="n"/>
       <c r="D75" s="8" t="n">
-        <v>1980.042</v>
+        <v>2778.9</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="20">
@@ -1619,7 +1637,7 @@
       </c>
       <c r="C76" s="18" t="n"/>
       <c r="D76" s="7" t="n">
-        <v>2676.983</v>
+        <v>3757.03</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="20">
@@ -1635,7 +1653,7 @@
       </c>
       <c r="C77" s="18" t="n"/>
       <c r="D77" s="8" t="n">
-        <v>3138.533</v>
+        <v>4404.8</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" s="20">
@@ -1651,7 +1669,7 @@
       </c>
       <c r="C78" s="18" t="n"/>
       <c r="D78" s="7" t="n">
-        <v>3674.439</v>
+        <v>5156.92</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="20">
@@ -1667,7 +1685,7 @@
       </c>
       <c r="C79" s="18" t="n"/>
       <c r="D79" s="7" t="n">
-        <v>3961.624</v>
+        <v>5559.98</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="20">
@@ -1683,9 +1701,10 @@
       </c>
       <c r="C80" s="18" t="n"/>
       <c r="D80" s="7" t="n">
-        <v>4043.966</v>
-      </c>
-    </row>
+        <v>5675.54</v>
+      </c>
+    </row>
+    <row r="81"/>
     <row r="82" ht="23.25" customHeight="1" s="20">
       <c r="A82" s="24" t="inlineStr">
         <is>
@@ -1693,6 +1712,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84" ht="18" customHeight="1" s="20">
       <c r="A84" s="9" t="inlineStr">
         <is>
@@ -1724,7 +1744,7 @@
       </c>
       <c r="C85" s="18" t="n"/>
       <c r="D85" s="7" t="n">
-        <v>1416.697</v>
+        <v>1988.27</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1" s="20">
@@ -1740,7 +1760,7 @@
       </c>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="8" t="n">
-        <v>1646.193</v>
+        <v>2310.36</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1" s="20">
@@ -1756,7 +1776,7 @@
       </c>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="7" t="n">
-        <v>1836.453</v>
+        <v>2577.38</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1" s="20">
@@ -1772,7 +1792,7 @@
       </c>
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="8" t="n">
-        <v>2023.122</v>
+        <v>2839.37</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1" s="20">
@@ -1788,7 +1808,7 @@
       </c>
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="7" t="n">
-        <v>2425.697</v>
+        <v>3404.36</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="20">
@@ -1804,7 +1824,7 @@
       </c>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="8" t="n">
-        <v>2539.032</v>
+        <v>3563.42</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="20">
@@ -1820,7 +1840,7 @@
       </c>
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="7" t="n">
-        <v>2994.939</v>
+        <v>4203.27</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="20">
@@ -1836,7 +1856,7 @@
       </c>
       <c r="C92" s="18" t="n"/>
       <c r="D92" s="8" t="n">
-        <v>3359.049</v>
+        <v>4714.29</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="20">
@@ -1852,7 +1872,7 @@
       </c>
       <c r="C93" s="18" t="n"/>
       <c r="D93" s="7" t="n">
-        <v>3974.448</v>
+        <v>5577.97</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="20">
@@ -1868,7 +1888,7 @@
       </c>
       <c r="C94" s="18" t="n"/>
       <c r="D94" s="8" t="n">
-        <v>4484.714</v>
+        <v>6294.11</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="20">
@@ -1884,7 +1904,7 @@
       </c>
       <c r="C95" s="18" t="n"/>
       <c r="D95" s="7" t="n">
-        <v>5479.608</v>
+        <v>7690.41</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="20">
@@ -1900,9 +1920,10 @@
       </c>
       <c r="C96" s="18" t="n"/>
       <c r="D96" s="7" t="n">
-        <v>7550.794</v>
-      </c>
-    </row>
+        <v>10597.23</v>
+      </c>
+    </row>
+    <row r="97"/>
     <row r="98" ht="23.25" customHeight="1" s="20">
       <c r="A98" s="24" t="inlineStr">
         <is>
@@ -1910,6 +1931,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100" ht="18" customHeight="1" s="20">
       <c r="A100" s="9" t="inlineStr">
         <is>
@@ -1941,7 +1963,7 @@
       </c>
       <c r="C101" s="18" t="n"/>
       <c r="D101" s="7" t="n">
-        <v>2143.638</v>
+        <v>3008.51</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1" s="20">
@@ -1957,7 +1979,7 @@
       </c>
       <c r="C102" s="18" t="n"/>
       <c r="D102" s="8" t="n">
-        <v>2425.697</v>
+        <v>3404.36</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1" s="20">
@@ -1973,7 +1995,7 @@
       </c>
       <c r="C103" s="18" t="n"/>
       <c r="D103" s="7" t="n">
-        <v>2738.521</v>
+        <v>3843.4</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1" s="20">
@@ -1989,7 +2011,7 @@
       </c>
       <c r="C104" s="18" t="n"/>
       <c r="D104" s="8" t="n">
-        <v>3246.228</v>
+        <v>4555.95</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1" s="20">
@@ -2005,7 +2027,7 @@
       </c>
       <c r="C105" s="18" t="n"/>
       <c r="D105" s="7" t="n">
-        <v>3282.125</v>
+        <v>4606.33</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1" s="20">
@@ -2021,7 +2043,7 @@
       </c>
       <c r="C106" s="18" t="n"/>
       <c r="D106" s="8" t="n">
-        <v>4146.244</v>
+        <v>5819.08</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1" s="20">
@@ -2037,7 +2059,7 @@
       </c>
       <c r="C107" s="18" t="n"/>
       <c r="D107" s="7" t="n">
-        <v>4666.772</v>
+        <v>6549.62</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1" s="20">
@@ -2053,7 +2075,7 @@
       </c>
       <c r="C108" s="18" t="n"/>
       <c r="D108" s="8" t="n">
-        <v>5269.353</v>
+        <v>7395.32</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1" s="20">
@@ -2069,7 +2091,7 @@
       </c>
       <c r="C109" s="18" t="n"/>
       <c r="D109" s="7" t="n">
-        <v>6102.7</v>
+        <v>8564.889999999999</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="20">
@@ -2085,9 +2107,10 @@
       </c>
       <c r="C110" s="18" t="n"/>
       <c r="D110" s="8" t="n">
-        <v>7777.371</v>
-      </c>
-    </row>
+        <v>10915.22</v>
+      </c>
+    </row>
+    <row r="111"/>
     <row r="112" ht="23.25" customHeight="1" s="20">
       <c r="A112" s="24" t="inlineStr">
         <is>
@@ -2095,6 +2118,7 @@
         </is>
       </c>
     </row>
+    <row r="113"/>
     <row r="114" ht="18" customHeight="1" s="20">
       <c r="A114" s="9" t="inlineStr">
         <is>
@@ -2126,7 +2150,7 @@
       </c>
       <c r="C115" s="18" t="n"/>
       <c r="D115" s="7" t="n">
-        <v>3075.712</v>
+        <v>4316.63</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="20">
@@ -2142,7 +2166,7 @@
       </c>
       <c r="C116" s="18" t="n"/>
       <c r="D116" s="8" t="n">
-        <v>3400.078</v>
+        <v>4771.87</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="20">
@@ -2158,7 +2182,7 @@
       </c>
       <c r="C117" s="18" t="n"/>
       <c r="D117" s="7" t="n">
-        <v>3948.807</v>
+        <v>5541.99</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1" s="20">
@@ -2174,7 +2198,7 @@
       </c>
       <c r="C118" s="18" t="n"/>
       <c r="D118" s="8" t="n">
-        <v>4100.091</v>
+        <v>5754.31</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="20">
@@ -2190,7 +2214,7 @@
       </c>
       <c r="C119" s="18" t="n"/>
       <c r="D119" s="7" t="n">
-        <v>4615.485</v>
+        <v>6477.64</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1" s="20">
@@ -2206,7 +2230,7 @@
       </c>
       <c r="C120" s="18" t="n"/>
       <c r="D120" s="8" t="n">
-        <v>5379.607</v>
+        <v>7550.06</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1" s="20">
@@ -2222,7 +2246,7 @@
       </c>
       <c r="C121" s="18" t="n"/>
       <c r="D121" s="7" t="n">
-        <v>6282.192</v>
+        <v>8816.799999999999</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1" s="20">
@@ -2238,7 +2262,7 @@
       </c>
       <c r="C122" s="18" t="n"/>
       <c r="D122" s="8" t="n">
-        <v>7102.722</v>
+        <v>9968.379999999999</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1" s="20">
@@ -2254,7 +2278,7 @@
       </c>
       <c r="C123" s="18" t="n"/>
       <c r="D123" s="7" t="n">
-        <v>7718.12</v>
+        <v>10832.07</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="20">
@@ -2270,9 +2294,11 @@
       </c>
       <c r="C124" s="18" t="n"/>
       <c r="D124" s="8" t="n">
-        <v>10419.458</v>
-      </c>
-    </row>
+        <v>14623.29</v>
+      </c>
+    </row>
+    <row r="125"/>
+    <row r="126"/>
     <row r="127" ht="20.25" customHeight="1" s="20">
       <c r="A127" s="14" t="inlineStr">
         <is>
@@ -2298,102 +2324,102 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="A128:B128"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B120:C120"/>
     <mergeCell ref="B121:C121"/>
     <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
     <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
     <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PARKER.xlsx
+++ b/LISTAS/ma/PARKER.xlsx
@@ -819,14 +819,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45264.54808382592</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="20">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,8 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="20">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -860,14 +854,6 @@
     <row r="12" ht="41.25" customHeight="1" s="20">
       <c r="A12" s="22" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21" ht="22.5" customHeight="1" s="20">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -911,7 +897,7 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="7" t="n">
-        <v>867.28</v>
+        <v>617.965</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="20">
@@ -927,7 +913,7 @@
       </c>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="8" t="n">
-        <v>896.0700000000001</v>
+        <v>638.478</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="20">
@@ -943,7 +929,7 @@
       </c>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="7" t="n">
-        <v>921.26</v>
+        <v>656.423</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="20">
@@ -959,7 +945,7 @@
       </c>
       <c r="C27" s="18" t="n"/>
       <c r="D27" s="8" t="n">
-        <v>983.52</v>
+        <v>700.783</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="20">
@@ -975,7 +961,7 @@
       </c>
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="7" t="n">
-        <v>1197.28</v>
+        <v>853.096</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="20">
@@ -991,7 +977,7 @@
       </c>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="8" t="n">
-        <v>1403.49</v>
+        <v>1000.023</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="20">
@@ -1007,7 +993,7 @@
       </c>
       <c r="C30" s="18" t="n"/>
       <c r="D30" s="8" t="n">
-        <v>1605.01</v>
+        <v>1143.613</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="20">
@@ -1023,7 +1009,7 @@
       </c>
       <c r="C31" s="18" t="n"/>
       <c r="D31" s="7" t="n">
-        <v>1734.57</v>
+        <v>1235.924</v>
       </c>
       <c r="E31" s="2" t="n"/>
     </row>
@@ -1071,7 +1057,7 @@
       </c>
       <c r="C36" s="18" t="n"/>
       <c r="D36" s="7" t="n">
-        <v>1110.2</v>
+        <v>791.045</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="20">
@@ -1087,7 +1073,7 @@
       </c>
       <c r="C37" s="18" t="n"/>
       <c r="D37" s="8" t="n">
-        <v>1219.23</v>
+        <v>868.736</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="20">
@@ -1103,7 +1089,7 @@
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="7" t="n">
-        <v>1291.2</v>
+        <v>920.0170000000001</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="20">
@@ -1119,7 +1105,7 @@
       </c>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="8" t="n">
-        <v>1369.3</v>
+        <v>975.664</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="20">
@@ -1135,7 +1121,7 @@
       </c>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="7" t="n">
-        <v>1529.44</v>
+        <v>1089.769</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="20">
@@ -1151,7 +1137,7 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="8" t="n">
-        <v>1986.48</v>
+        <v>1415.417</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="20">
@@ -1167,7 +1153,7 @@
       </c>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="7" t="n">
-        <v>2008.07</v>
+        <v>1430.801</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="20">
@@ -1183,7 +1169,7 @@
       </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="8" t="n">
-        <v>2058.45</v>
+        <v>1466.7</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="20">
@@ -1199,7 +1185,7 @@
       </c>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="7" t="n">
-        <v>2627.05</v>
+        <v>1871.839</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="20">
@@ -1215,7 +1201,7 @@
       </c>
       <c r="C45" s="18" t="n"/>
       <c r="D45" s="8" t="n">
-        <v>3084.08</v>
+        <v>2197.487</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="20">
@@ -1231,7 +1217,7 @@
       </c>
       <c r="C46" s="18" t="n"/>
       <c r="D46" s="7" t="n">
-        <v>3778.63</v>
+        <v>2692.371</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="20">
@@ -1247,10 +1233,9 @@
       </c>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="7" t="n">
-        <v>4325.62</v>
-      </c>
-    </row>
-    <row r="48"/>
+        <v>3082.117</v>
+      </c>
+    </row>
     <row r="49" ht="23.25" customHeight="1" s="20">
       <c r="A49" s="24" t="inlineStr">
         <is>
@@ -1258,7 +1243,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="18" customHeight="1" s="20">
       <c r="A51" s="9" t="inlineStr">
         <is>
@@ -1290,7 +1274,7 @@
       </c>
       <c r="C52" s="18" t="n"/>
       <c r="D52" s="7" t="n">
-        <v>1183.97</v>
+        <v>843.61</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="20">
@@ -1306,7 +1290,7 @@
       </c>
       <c r="C53" s="18" t="n"/>
       <c r="D53" s="8" t="n">
-        <v>1425.08</v>
+        <v>1015.406</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="20">
@@ -1322,7 +1306,7 @@
       </c>
       <c r="C54" s="18" t="n"/>
       <c r="D54" s="7" t="n">
-        <v>1565.43</v>
+        <v>1115.411</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="20">
@@ -1338,7 +1322,7 @@
       </c>
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="8" t="n">
-        <v>1705.78</v>
+        <v>1215.414</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="20">
@@ -1354,7 +1338,7 @@
       </c>
       <c r="C56" s="18" t="n"/>
       <c r="D56" s="7" t="n">
-        <v>1853.33</v>
+        <v>1320.543</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="20">
@@ -1370,7 +1354,7 @@
       </c>
       <c r="C57" s="18" t="n"/>
       <c r="D57" s="8" t="n">
-        <v>2058.45</v>
+        <v>1466.7</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="20">
@@ -1386,7 +1370,7 @@
       </c>
       <c r="C58" s="18" t="n"/>
       <c r="D58" s="7" t="n">
-        <v>2213.2</v>
+        <v>1576.961</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="20">
@@ -1402,7 +1386,7 @@
       </c>
       <c r="C59" s="18" t="n"/>
       <c r="D59" s="8" t="n">
-        <v>2400.33</v>
+        <v>1710.297</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="20">
@@ -1418,7 +1402,7 @@
       </c>
       <c r="C60" s="18" t="n"/>
       <c r="D60" s="7" t="n">
-        <v>3547.59</v>
+        <v>2527.749</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="20">
@@ -1434,7 +1418,7 @@
       </c>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="8" t="n">
-        <v>3839.81</v>
+        <v>2735.962</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="20">
@@ -1450,7 +1434,7 @@
       </c>
       <c r="C62" s="18" t="n"/>
       <c r="D62" s="7" t="n">
-        <v>4271.65</v>
+        <v>3043.659</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1" s="20">
@@ -1466,10 +1450,9 @@
       </c>
       <c r="C63" s="18" t="n"/>
       <c r="D63" s="7" t="n">
-        <v>5124.54</v>
-      </c>
-    </row>
-    <row r="64"/>
+        <v>3651.367</v>
+      </c>
+    </row>
     <row r="65" ht="23.25" customHeight="1" s="20">
       <c r="A65" s="24" t="inlineStr">
         <is>
@@ -1477,7 +1460,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67" ht="18" customHeight="1" s="20">
       <c r="A67" s="9" t="inlineStr">
         <is>
@@ -1509,7 +1491,7 @@
       </c>
       <c r="C68" s="18" t="n"/>
       <c r="D68" s="7" t="n">
-        <v>1422.2</v>
+        <v>1013.358</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="20">
@@ -1525,7 +1507,7 @@
       </c>
       <c r="C69" s="18" t="n"/>
       <c r="D69" s="8" t="n">
-        <v>1635.24</v>
+        <v>1165.152</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="20">
@@ -1541,7 +1523,7 @@
       </c>
       <c r="C70" s="18" t="n"/>
       <c r="D70" s="7" t="n">
-        <v>1705.78</v>
+        <v>1215.414</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="20">
@@ -1557,7 +1539,7 @@
       </c>
       <c r="C71" s="18" t="n"/>
       <c r="D71" s="8" t="n">
-        <v>1853.33</v>
+        <v>1320.543</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="20">
@@ -1573,7 +1555,7 @@
       </c>
       <c r="C72" s="18" t="n"/>
       <c r="D72" s="7" t="n">
-        <v>2109.92</v>
+        <v>1503.37</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="20">
@@ -1589,7 +1571,7 @@
       </c>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="8" t="n">
-        <v>2281.57</v>
+        <v>1625.677</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="20">
@@ -1605,7 +1587,7 @@
       </c>
       <c r="C74" s="18" t="n"/>
       <c r="D74" s="7" t="n">
-        <v>2501.09</v>
+        <v>1782.092</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="20">
@@ -1621,7 +1603,7 @@
       </c>
       <c r="C75" s="18" t="n"/>
       <c r="D75" s="8" t="n">
-        <v>2778.9</v>
+        <v>1980.042</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="20">
@@ -1637,7 +1619,7 @@
       </c>
       <c r="C76" s="18" t="n"/>
       <c r="D76" s="7" t="n">
-        <v>3757.03</v>
+        <v>2676.983</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="20">
@@ -1653,7 +1635,7 @@
       </c>
       <c r="C77" s="18" t="n"/>
       <c r="D77" s="8" t="n">
-        <v>4404.8</v>
+        <v>3138.533</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" s="20">
@@ -1669,7 +1651,7 @@
       </c>
       <c r="C78" s="18" t="n"/>
       <c r="D78" s="7" t="n">
-        <v>5156.92</v>
+        <v>3674.439</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="20">
@@ -1685,7 +1667,7 @@
       </c>
       <c r="C79" s="18" t="n"/>
       <c r="D79" s="7" t="n">
-        <v>5559.98</v>
+        <v>3961.624</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="20">
@@ -1704,7 +1686,6 @@
         <v>5675.54</v>
       </c>
     </row>
-    <row r="81"/>
     <row r="82" ht="23.25" customHeight="1" s="20">
       <c r="A82" s="24" t="inlineStr">
         <is>
@@ -1712,7 +1693,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84" ht="18" customHeight="1" s="20">
       <c r="A84" s="9" t="inlineStr">
         <is>
@@ -1744,7 +1724,7 @@
       </c>
       <c r="C85" s="18" t="n"/>
       <c r="D85" s="7" t="n">
-        <v>1988.27</v>
+        <v>1416.697</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1" s="20">
@@ -1760,7 +1740,7 @@
       </c>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="8" t="n">
-        <v>2310.36</v>
+        <v>1646.193</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1" s="20">
@@ -1776,7 +1756,7 @@
       </c>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="7" t="n">
-        <v>2577.38</v>
+        <v>1836.453</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1" s="20">
@@ -1792,7 +1772,7 @@
       </c>
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="8" t="n">
-        <v>2839.37</v>
+        <v>2023.122</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1" s="20">
@@ -1808,7 +1788,7 @@
       </c>
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="7" t="n">
-        <v>3404.36</v>
+        <v>2425.697</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="20">
@@ -1824,7 +1804,7 @@
       </c>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="8" t="n">
-        <v>3563.42</v>
+        <v>2539.032</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="20">
@@ -1840,7 +1820,7 @@
       </c>
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="7" t="n">
-        <v>4203.27</v>
+        <v>2994.939</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="20">
@@ -1856,7 +1836,7 @@
       </c>
       <c r="C92" s="18" t="n"/>
       <c r="D92" s="8" t="n">
-        <v>4714.29</v>
+        <v>3359.049</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="20">
@@ -1872,7 +1852,7 @@
       </c>
       <c r="C93" s="18" t="n"/>
       <c r="D93" s="7" t="n">
-        <v>5577.97</v>
+        <v>3974.448</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="20">
@@ -1888,7 +1868,7 @@
       </c>
       <c r="C94" s="18" t="n"/>
       <c r="D94" s="8" t="n">
-        <v>6294.11</v>
+        <v>4484.714</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="20">
@@ -1904,7 +1884,7 @@
       </c>
       <c r="C95" s="18" t="n"/>
       <c r="D95" s="7" t="n">
-        <v>7690.41</v>
+        <v>5479.608</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="20">
@@ -1923,7 +1903,6 @@
         <v>10597.23</v>
       </c>
     </row>
-    <row r="97"/>
     <row r="98" ht="23.25" customHeight="1" s="20">
       <c r="A98" s="24" t="inlineStr">
         <is>
@@ -1931,7 +1910,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100" ht="18" customHeight="1" s="20">
       <c r="A100" s="9" t="inlineStr">
         <is>
@@ -1963,7 +1941,7 @@
       </c>
       <c r="C101" s="18" t="n"/>
       <c r="D101" s="7" t="n">
-        <v>3008.51</v>
+        <v>2143.638</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1" s="20">
@@ -1979,7 +1957,7 @@
       </c>
       <c r="C102" s="18" t="n"/>
       <c r="D102" s="8" t="n">
-        <v>3404.36</v>
+        <v>2425.697</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1" s="20">
@@ -1995,7 +1973,7 @@
       </c>
       <c r="C103" s="18" t="n"/>
       <c r="D103" s="7" t="n">
-        <v>3843.4</v>
+        <v>2738.521</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1" s="20">
@@ -2011,7 +1989,7 @@
       </c>
       <c r="C104" s="18" t="n"/>
       <c r="D104" s="8" t="n">
-        <v>4555.95</v>
+        <v>3246.228</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1" s="20">
@@ -2027,7 +2005,7 @@
       </c>
       <c r="C105" s="18" t="n"/>
       <c r="D105" s="7" t="n">
-        <v>4606.33</v>
+        <v>3282.125</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1" s="20">
@@ -2043,7 +2021,7 @@
       </c>
       <c r="C106" s="18" t="n"/>
       <c r="D106" s="8" t="n">
-        <v>5819.08</v>
+        <v>4146.244</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1" s="20">
@@ -2059,7 +2037,7 @@
       </c>
       <c r="C107" s="18" t="n"/>
       <c r="D107" s="7" t="n">
-        <v>6549.62</v>
+        <v>4666.772</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1" s="20">
@@ -2075,7 +2053,7 @@
       </c>
       <c r="C108" s="18" t="n"/>
       <c r="D108" s="8" t="n">
-        <v>7395.32</v>
+        <v>5269.353</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1" s="20">
@@ -2091,7 +2069,7 @@
       </c>
       <c r="C109" s="18" t="n"/>
       <c r="D109" s="7" t="n">
-        <v>8564.889999999999</v>
+        <v>6102.7</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="20">
@@ -2110,7 +2088,6 @@
         <v>10915.22</v>
       </c>
     </row>
-    <row r="111"/>
     <row r="112" ht="23.25" customHeight="1" s="20">
       <c r="A112" s="24" t="inlineStr">
         <is>
@@ -2118,7 +2095,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114" ht="18" customHeight="1" s="20">
       <c r="A114" s="9" t="inlineStr">
         <is>
@@ -2150,7 +2126,7 @@
       </c>
       <c r="C115" s="18" t="n"/>
       <c r="D115" s="7" t="n">
-        <v>4316.63</v>
+        <v>3075.712</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="20">
@@ -2166,7 +2142,7 @@
       </c>
       <c r="C116" s="18" t="n"/>
       <c r="D116" s="8" t="n">
-        <v>4771.87</v>
+        <v>3400.078</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="20">
@@ -2182,7 +2158,7 @@
       </c>
       <c r="C117" s="18" t="n"/>
       <c r="D117" s="7" t="n">
-        <v>5541.99</v>
+        <v>3948.807</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1" s="20">
@@ -2198,7 +2174,7 @@
       </c>
       <c r="C118" s="18" t="n"/>
       <c r="D118" s="8" t="n">
-        <v>5754.31</v>
+        <v>4100.091</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="20">
@@ -2214,7 +2190,7 @@
       </c>
       <c r="C119" s="18" t="n"/>
       <c r="D119" s="7" t="n">
-        <v>6477.64</v>
+        <v>4615.485</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1" s="20">
@@ -2230,7 +2206,7 @@
       </c>
       <c r="C120" s="18" t="n"/>
       <c r="D120" s="8" t="n">
-        <v>7550.06</v>
+        <v>5379.607</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1" s="20">
@@ -2246,7 +2222,7 @@
       </c>
       <c r="C121" s="18" t="n"/>
       <c r="D121" s="7" t="n">
-        <v>8816.799999999999</v>
+        <v>6282.192</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1" s="20">
@@ -2262,7 +2238,7 @@
       </c>
       <c r="C122" s="18" t="n"/>
       <c r="D122" s="8" t="n">
-        <v>9968.379999999999</v>
+        <v>7102.722</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1" s="20">
@@ -2278,7 +2254,7 @@
       </c>
       <c r="C123" s="18" t="n"/>
       <c r="D123" s="7" t="n">
-        <v>10832.07</v>
+        <v>7718.12</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="20">
@@ -2297,8 +2273,6 @@
         <v>14623.29</v>
       </c>
     </row>
-    <row r="125"/>
-    <row r="126"/>
     <row r="127" ht="20.25" customHeight="1" s="20">
       <c r="A127" s="14" t="inlineStr">
         <is>
@@ -2324,102 +2298,102 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
     <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
